--- a/Excel/FirstWinConfig.xlsx
+++ b/Excel/FirstWinConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{856E5355-3651-4C47-BCA6-2A4CED242013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AF985DA-81BE-4A35-9DE4-664E8C67DDA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FirstWinProto" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="47">
   <si>
     <t>Id</t>
   </si>
@@ -1515,7 +1515,43 @@
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
     </row>
-    <row r="28" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1">
+        <v>60004</v>
+      </c>
+      <c r="D28" s="1">
+        <v>6</v>
+      </c>
+      <c r="E28" s="1">
+        <v>70006014</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+    </row>
     <row r="29" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="30" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="31" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
